--- a/survey_templates/043_student_clubs_survey--survey_templates.xlsx
+++ b/survey_templates/043_student_clubs_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -799,7 +799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -861,34 +861,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>activities_choices</t>
+          <t>club_condition_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>meetings</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Meetings</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>activities_choices</t>
+          <t>club_condition_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>events</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Events</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -900,46 +900,46 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>club_condition_choices</t>
+          <t>club_meeting_time_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>club_condition_choices</t>
+          <t>club_meeting_time_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>bi-weekly</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Bi-Weekly</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -968,46 +968,46 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>bi-weekly</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bi-Weekly</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>club_meeting_time_choices</t>
+          <t>meeting_location_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>cafeteria</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Cafeteria</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>club_meeting_time_choices</t>
+          <t>meeting_location_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>library</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Library</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>cafeteria</t>
+          <t>classroom</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cafeteria</t>
+          <t>Classroom</t>
         </is>
       </c>
     </row>
@@ -1036,44 +1036,10 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>library</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
-        <is>
-          <t>Library</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>meeting_location_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>classroom</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Classroom</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>meeting_location_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
